--- a/artfynd/Tutvikskogens naturreservat artfynd.xlsx
+++ b/artfynd/Tutvikskogens naturreservat artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY353"/>
+  <dimension ref="A1:AZ353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112827726</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112827863</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87072501</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1091,6 +1111,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112253465</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112299569</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1305,6 +1335,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112299575</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1412,6 +1447,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112299571</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1519,6 +1559,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112299576</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1636,6 +1681,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104622410</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1753,6 +1803,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104622530</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1860,6 +1915,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112299570</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1967,6 +2027,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112299572</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2068,6 +2133,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112827770</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2185,6 +2255,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104622873</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2286,6 +2361,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112253475</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2387,6 +2467,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112253480</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2488,6 +2573,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112253489</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2595,6 +2685,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112299594</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2712,6 +2807,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104622755</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2813,6 +2913,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119921800</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2920,6 +3025,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112299593</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3032,6 +3142,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104622512</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3139,6 +3254,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112299595</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3240,6 +3360,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112253470</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3357,6 +3482,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104622958</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3468,6 +3598,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112827896</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3581,6 +3716,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104607550</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3694,6 +3834,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104607508</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3809,6 +3954,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77140159</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3917,6 +4067,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104607334</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4030,6 +4185,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104607151</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4150,6 +4310,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77140193</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4251,6 +4416,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112116944</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4352,6 +4522,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112116990</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4453,6 +4628,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112117043</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4560,6 +4740,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923138</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4667,6 +4852,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923151</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4774,6 +4964,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112299583</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4875,6 +5070,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119921742</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4976,6 +5176,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119921749</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5083,6 +5288,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923146</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5200,6 +5410,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104607015</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5317,6 +5532,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104607049</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5424,6 +5644,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112299582</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5536,6 +5761,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104607102</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5642,6 +5872,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124244473</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5749,6 +5984,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923143</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5850,6 +6090,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112116908</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5951,6 +6196,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112253709</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6070,6 +6320,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112299591</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6177,6 +6432,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87072500</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6285,6 +6545,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104613342</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6393,6 +6658,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104613405</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6500,6 +6770,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112299579</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6607,6 +6882,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112299592</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6708,6 +6988,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112116915</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6809,6 +7094,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112253460</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6927,6 +7217,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119914730</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7028,6 +7323,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112116930</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7129,6 +7429,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112220497</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7230,6 +7535,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112253456</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7338,6 +7648,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104613395</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7456,6 +7771,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119915210</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7563,6 +7883,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112299578</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7680,6 +8005,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104623405</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7786,6 +8116,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106161291</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7913,6 +8248,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923096</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8030,6 +8370,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104613209</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8147,6 +8492,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104613290</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8255,6 +8605,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104623132</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8382,6 +8737,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112300384</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8483,6 +8843,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112827933</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8584,6 +8949,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112220554</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8685,6 +9055,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112220534</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8786,6 +9161,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112253722</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8903,6 +9283,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104623465</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9020,6 +9405,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104623524</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9137,6 +9527,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104623939</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9238,6 +9633,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120189980</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9355,6 +9755,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104623625</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9472,6 +9877,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104623645</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9580,6 +9990,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104623477</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9689,6 +10104,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71225807</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9798,6 +10218,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71225824</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9899,6 +10324,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120189971</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10000,6 +10430,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112253394</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10117,6 +10552,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104608250</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10218,6 +10658,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112253343</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10319,6 +10764,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112253347</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10420,6 +10870,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112253369</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10517,6 +10972,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119909539</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10614,6 +11074,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119910526</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10721,6 +11186,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923120</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10828,6 +11298,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923125</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10929,6 +11404,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112117062</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11036,6 +11516,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923117</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11143,6 +11628,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923119</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11250,6 +11740,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923123</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11362,6 +11857,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104608887</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11473,6 +11973,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923115</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11574,6 +12079,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112253358</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11691,6 +12201,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104608587</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11799,6 +12314,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104608859</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11916,6 +12436,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104609037</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12043,6 +12568,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923121</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12155,6 +12685,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923116</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12265,6 +12800,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119921766</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12366,6 +12906,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112117017</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12473,6 +13018,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923133</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12580,6 +13130,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923137</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12687,6 +13242,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923108</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12794,6 +13354,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923132</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12895,6 +13460,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112116834</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12996,6 +13566,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112117005</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13108,6 +13683,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104609568</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13215,6 +13795,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923134</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13332,6 +13917,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104609878</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13433,6 +14023,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106176488</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13560,6 +14155,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923127</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13668,6 +14268,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104609946</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13775,6 +14380,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112299584</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13876,6 +14486,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112117067</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13984,6 +14599,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104609459</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14092,6 +14712,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104609810</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14219,6 +14844,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923129</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14331,6 +14961,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923130</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14443,6 +15078,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923126</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14555,6 +15195,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923128</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14667,6 +15312,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923136</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14775,6 +15425,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104609905</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14882,6 +15537,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923109</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14983,6 +15643,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105522389</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15084,6 +15749,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112116846</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15185,6 +15855,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112116871</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15286,6 +15961,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112116883</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15387,6 +16067,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112220565</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15488,6 +16173,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112122275</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15589,6 +16279,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112356606</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15706,6 +16401,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104631603</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15813,6 +16513,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112299586</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15920,6 +16625,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112299590</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16027,6 +16737,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923098</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16134,6 +16849,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923103</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16235,6 +16955,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112116855</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16347,6 +17072,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104631452</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16464,6 +17194,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104631484</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16576,6 +17311,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104631511</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16693,6 +17433,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104631537</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16805,6 +17550,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104631820</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16912,6 +17662,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923101</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17019,6 +17774,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923102</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17126,6 +17886,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923104</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17227,6 +17992,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106176483</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17354,6 +18124,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923105</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17455,6 +18230,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112116698</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17556,6 +18336,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112827949</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17673,6 +18458,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104631361</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17790,6 +18580,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104631387</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17897,6 +18692,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112299585</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18009,6 +18809,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112299587</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18110,6 +18915,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120190005</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18211,6 +19021,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112220418</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18328,6 +19143,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104631376</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18445,6 +19265,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104631414</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18554,6 +19379,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112827616</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18666,6 +19496,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923097</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18768,6 +19603,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112116689</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18869,6 +19709,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112253731</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18970,6 +19815,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120189965</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19071,6 +19921,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120189989</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19172,6 +20027,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112220456</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19289,6 +20149,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104624100</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -19406,6 +20271,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104624236</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -19523,6 +20393,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104624317</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -19644,6 +20519,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/35452589</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19768,6 +20648,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86109748</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19887,6 +20772,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97168372</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20004,6 +20894,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104610211</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20121,6 +21016,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104610099</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -20248,6 +21148,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923113</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -20349,6 +21254,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112117070</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -20450,6 +21360,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112117126</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -20551,6 +21466,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112253325</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -20659,6 +21579,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104610437</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -20766,6 +21691,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923111</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -20873,6 +21803,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923112</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -20974,6 +21909,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112116803</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -21075,6 +22015,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112117103</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -21176,6 +22121,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120021564</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -21283,6 +22233,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923110</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -21400,6 +22355,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104610390</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -21517,6 +22477,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104610500</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -21624,6 +22589,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134458701</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -21735,6 +22705,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134458808</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -21840,6 +22815,11 @@
           <t>Fynd med DNA-sekvens - extern</t>
         </is>
       </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118843525</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -21941,6 +22921,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112116769</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -22042,6 +23027,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112207718</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -22143,6 +23133,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112207768</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -22244,6 +23239,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112220577</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -22345,6 +23345,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112930610</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -22452,6 +23457,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923107</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -22557,6 +23567,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120021524</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -22672,6 +23687,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83949959</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -22769,6 +23789,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124748010</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -22881,6 +23906,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124748231</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -22988,6 +24018,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789086</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -23098,6 +24133,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81778668</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -23199,6 +24239,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112116671</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -23300,6 +24345,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112116717</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -23408,6 +24458,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104612557</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -23525,6 +24580,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104612675</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -23626,6 +24686,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112207731</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -23733,6 +24798,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923106</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -23834,6 +24904,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120021541</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -23935,6 +25010,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120021786</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -24049,6 +25129,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93503208</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -24163,6 +25248,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77139988</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -24290,6 +25380,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789084</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -24422,6 +25517,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789085</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -24523,6 +25623,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112207751</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -24624,6 +25729,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124244532</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -24741,6 +25851,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104612551</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -24858,6 +25973,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104612622</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -24968,6 +26088,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124748133</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -25065,6 +26190,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838746</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -25179,6 +26309,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77139968</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -25276,6 +26411,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124747576</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -25383,6 +26523,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789089</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -25484,6 +26629,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112827957</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -25585,6 +26735,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120190016</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -25717,6 +26872,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789088</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -25827,6 +26987,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104666939</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -25935,6 +27100,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104628160</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -26043,6 +27213,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104628212</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -26151,6 +27326,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104628280</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -26266,6 +27446,11 @@
           <t>Floraväkteri AB-län</t>
         </is>
       </c>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114731</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -26391,6 +27576,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114732</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -26500,6 +27690,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113293284</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -26615,6 +27810,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134458631</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -26716,6 +27916,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112253288</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -26823,6 +28028,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789082</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -26931,6 +28141,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104610823</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -27032,6 +28247,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112207694</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -27144,6 +28364,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789081</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -27241,6 +28466,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838745</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -27373,6 +28603,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789083</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -27475,6 +28710,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105282199</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -27586,6 +28826,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124744539</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -27701,6 +28946,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124744553</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -27798,6 +29048,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124744652</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -27905,6 +29160,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789080</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -28012,6 +29272,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789100</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -28109,6 +29374,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838765</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -28206,6 +29476,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838767</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -28307,6 +29582,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112253809</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -28408,6 +29688,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112253896</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -28525,6 +29810,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104612372</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -28637,6 +29927,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104612390</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -28745,6 +30040,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104612400</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -28846,6 +30146,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112207703</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -28947,6 +30252,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120021740</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -29074,6 +30384,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789101</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -29171,6 +30486,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838756</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -29283,6 +30603,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789098</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -29384,6 +30709,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112827601</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -29492,6 +30822,11 @@
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104612289</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -29609,6 +30944,11 @@
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104612318</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -29726,6 +31066,11 @@
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104612330</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -29853,6 +31198,11 @@
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789099</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -29950,6 +31300,11 @@
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838747</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -30047,6 +31402,11 @@
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838748</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -30163,6 +31523,11 @@
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124744604</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -30260,6 +31625,11 @@
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838751</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -30361,6 +31731,11 @@
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112220326</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -30462,6 +31837,11 @@
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120189952</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -30563,6 +31943,11 @@
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120189913</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -30670,6 +32055,11 @@
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124744322</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -30797,6 +32187,11 @@
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789090</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -30924,6 +32319,11 @@
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789091</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -31021,6 +32421,11 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838754</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -31118,6 +32523,11 @@
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838755</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -31215,6 +32625,11 @@
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838744</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -31339,6 +32754,11 @@
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112985219</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -31440,6 +32860,11 @@
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120189921</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -31541,6 +32966,11 @@
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120189929</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -31646,6 +33076,11 @@
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120190094</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -31754,6 +33189,11 @@
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104630426</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -31862,6 +33302,11 @@
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104630624</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -31970,6 +33415,11 @@
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104630709</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -32097,6 +33547,11 @@
         </is>
       </c>
       <c r="AY291" t="inlineStr"/>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789093</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -32214,6 +33669,11 @@
         </is>
       </c>
       <c r="AY292" t="inlineStr"/>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789097</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -32326,6 +33786,11 @@
         </is>
       </c>
       <c r="AY293" t="inlineStr"/>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124744770</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -32445,6 +33910,11 @@
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124746306</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -32577,6 +34047,11 @@
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789094</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -32709,6 +34184,11 @@
         </is>
       </c>
       <c r="AY296" t="inlineStr"/>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789095</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -32806,6 +34286,11 @@
         </is>
       </c>
       <c r="AY297" t="inlineStr"/>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838759</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -32922,6 +34407,11 @@
         </is>
       </c>
       <c r="AY298" t="inlineStr"/>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124746091</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -33029,6 +34519,11 @@
         </is>
       </c>
       <c r="AY299" t="inlineStr"/>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122398872</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -33126,6 +34621,11 @@
         </is>
       </c>
       <c r="AY300" t="inlineStr"/>
+      <c r="AZ300" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124745159</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -33237,6 +34737,11 @@
         </is>
       </c>
       <c r="AY301" t="inlineStr"/>
+      <c r="AZ301" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124745402</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -33344,6 +34849,11 @@
         </is>
       </c>
       <c r="AY302" t="inlineStr"/>
+      <c r="AZ302" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789096</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -33441,6 +34951,11 @@
         </is>
       </c>
       <c r="AY303" t="inlineStr"/>
+      <c r="AZ303" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124745146</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -33547,6 +35062,11 @@
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
+      <c r="AZ304" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105447692</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -33649,6 +35169,11 @@
         </is>
       </c>
       <c r="AY305" t="inlineStr"/>
+      <c r="AZ305" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67042975</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -33757,6 +35282,11 @@
         </is>
       </c>
       <c r="AY306" t="inlineStr"/>
+      <c r="AZ306" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104629916</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -33862,6 +35392,11 @@
         </is>
       </c>
       <c r="AY307" t="inlineStr"/>
+      <c r="AZ307" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120189903</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -33979,6 +35514,11 @@
         </is>
       </c>
       <c r="AY308" t="inlineStr"/>
+      <c r="AZ308" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104629869</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -34087,6 +35627,11 @@
         </is>
       </c>
       <c r="AY309" t="inlineStr"/>
+      <c r="AZ309" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104630124</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -34214,6 +35759,11 @@
         </is>
       </c>
       <c r="AY310" t="inlineStr"/>
+      <c r="AZ310" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789115</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -34311,6 +35861,11 @@
         </is>
       </c>
       <c r="AY311" t="inlineStr"/>
+      <c r="AZ311" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838750</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -34427,6 +35982,11 @@
         </is>
       </c>
       <c r="AY312" t="inlineStr"/>
+      <c r="AZ312" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124737438</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -34543,6 +36103,11 @@
         </is>
       </c>
       <c r="AY313" t="inlineStr"/>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124737727</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -34675,6 +36240,11 @@
         </is>
       </c>
       <c r="AY314" t="inlineStr"/>
+      <c r="AZ314" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789116</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -34781,6 +36351,11 @@
         </is>
       </c>
       <c r="AY315" t="inlineStr"/>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106176472</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -34882,6 +36457,11 @@
         </is>
       </c>
       <c r="AY316" t="inlineStr"/>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107311392</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -35009,6 +36589,11 @@
         </is>
       </c>
       <c r="AY317" t="inlineStr"/>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789111</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -35106,6 +36691,11 @@
         </is>
       </c>
       <c r="AY318" t="inlineStr"/>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838752</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -35203,6 +36793,11 @@
         </is>
       </c>
       <c r="AY319" t="inlineStr"/>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838753</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -35314,6 +36909,11 @@
         </is>
       </c>
       <c r="AY320" t="inlineStr"/>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124740044</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -35421,6 +37021,11 @@
         </is>
       </c>
       <c r="AY321" t="inlineStr"/>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789107</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -35522,6 +37127,11 @@
         </is>
       </c>
       <c r="AY322" t="inlineStr"/>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112116647</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -35623,6 +37233,11 @@
         </is>
       </c>
       <c r="AY323" t="inlineStr"/>
+      <c r="AZ323" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112930604</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -35733,6 +37348,11 @@
         </is>
       </c>
       <c r="AY324" t="inlineStr"/>
+      <c r="AZ324" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124742759</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -35860,6 +37480,11 @@
         </is>
       </c>
       <c r="AY325" t="inlineStr"/>
+      <c r="AZ325" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789103</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -35987,6 +37612,11 @@
         </is>
       </c>
       <c r="AY326" t="inlineStr"/>
+      <c r="AZ326" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789104</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -36088,6 +37718,11 @@
         </is>
       </c>
       <c r="AY327" t="inlineStr"/>
+      <c r="AZ327" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107311425</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -36196,6 +37831,11 @@
         </is>
       </c>
       <c r="AY328" t="inlineStr"/>
+      <c r="AZ328" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104612079</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -36313,6 +37953,11 @@
         </is>
       </c>
       <c r="AY329" t="inlineStr"/>
+      <c r="AZ329" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104612179</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -36440,6 +38085,11 @@
         </is>
       </c>
       <c r="AY330" t="inlineStr"/>
+      <c r="AZ330" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789108</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -36567,6 +38217,11 @@
         </is>
       </c>
       <c r="AY331" t="inlineStr"/>
+      <c r="AZ331" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789110</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -36664,6 +38319,11 @@
         </is>
       </c>
       <c r="AY332" t="inlineStr"/>
+      <c r="AZ332" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838749</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -36781,6 +38441,11 @@
         </is>
       </c>
       <c r="AY333" t="inlineStr"/>
+      <c r="AZ333" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789106</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -36888,6 +38553,11 @@
         </is>
       </c>
       <c r="AY334" t="inlineStr"/>
+      <c r="AZ334" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120021579</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -37000,6 +38670,11 @@
         </is>
       </c>
       <c r="AY335" t="inlineStr"/>
+      <c r="AZ335" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124739662</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -37107,6 +38782,11 @@
         </is>
       </c>
       <c r="AY336" t="inlineStr"/>
+      <c r="AZ336" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124743172</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -37224,6 +38904,11 @@
         </is>
       </c>
       <c r="AY337" t="inlineStr"/>
+      <c r="AZ337" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789109</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -37356,6 +39041,11 @@
         </is>
       </c>
       <c r="AY338" t="inlineStr"/>
+      <c r="AZ338" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789078</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -37472,6 +39162,11 @@
         </is>
       </c>
       <c r="AY339" t="inlineStr"/>
+      <c r="AZ339" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124739562</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -37588,6 +39283,11 @@
         </is>
       </c>
       <c r="AY340" t="inlineStr"/>
+      <c r="AZ340" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124743869</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -37685,6 +39385,11 @@
         </is>
       </c>
       <c r="AY341" t="inlineStr"/>
+      <c r="AZ341" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838760</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -37801,6 +39506,11 @@
         </is>
       </c>
       <c r="AY342" t="inlineStr"/>
+      <c r="AZ342" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124739648</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -37917,6 +39627,11 @@
         </is>
       </c>
       <c r="AY343" t="inlineStr"/>
+      <c r="AZ343" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124740386</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -38049,6 +39764,11 @@
         </is>
       </c>
       <c r="AY344" t="inlineStr"/>
+      <c r="AZ344" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789079</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -38146,6 +39866,11 @@
         </is>
       </c>
       <c r="AY345" t="inlineStr"/>
+      <c r="AZ345" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838768</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -38252,6 +39977,11 @@
         </is>
       </c>
       <c r="AY346" t="inlineStr"/>
+      <c r="AZ346" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106161310</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -38359,6 +40089,11 @@
         </is>
       </c>
       <c r="AY347" t="inlineStr"/>
+      <c r="AZ347" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124744240</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -38460,6 +40195,11 @@
         </is>
       </c>
       <c r="AY348" t="inlineStr"/>
+      <c r="AZ348" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120190103</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -38561,6 +40301,11 @@
         </is>
       </c>
       <c r="AY349" t="inlineStr"/>
+      <c r="AZ349" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120523054</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -38673,6 +40418,11 @@
         </is>
       </c>
       <c r="AY350" t="inlineStr"/>
+      <c r="AZ350" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124744085</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -38774,6 +40524,11 @@
         </is>
       </c>
       <c r="AY351" t="inlineStr"/>
+      <c r="AZ351" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112930585</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -38906,6 +40661,11 @@
         </is>
       </c>
       <c r="AY352" t="inlineStr"/>
+      <c r="AZ352" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789113</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -39038,8 +40798,367 @@
         </is>
       </c>
       <c r="AY353" t="inlineStr"/>
+      <c r="AZ353" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124789112</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ340" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ341" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ342" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ343" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ344" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ345" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ346" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ347" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ348" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ350" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ351" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ353" r:id="rId352"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>